--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F4" t="n">
+        <v>2.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>24/08 13:15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F15" t="n">
+        <v>4.25</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
+      <c r="F16" t="n">
+        <v>5.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+      <c r="F17" t="n">
+        <v>1.82</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>24/08 01:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>18/08 18:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>18/08 19:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>6.20</t>
-        </is>
+      <c r="F22" t="n">
+        <v>6.2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>55</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>26/08 00:15</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>27/08 13:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>20</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45887.08225903788</v>
+        <v>45887.08225903935</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Arda KardzhaliLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+6,45%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45887.1550627274</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | Plus que 2.5 | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mirassol – CruzeiroBrésil - Série A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 2.5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>18/08 23:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+2,81%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45887.1550627274</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Plus que 8.52e participant | Iga Swiate</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Iga Swiatek – J PaoliniWTA Cincinnati 2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 8.52e participant</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>18/08 22:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,43%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45887.1550627274</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Crystal Palace – FredrikstadLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+1,08%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45887.1550627274</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>40</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45887.1550627274</v>
+        <v>45887.15506273148</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>18/08 23:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45887.1550627274</v>
+        <v>45887.15506273148</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>18/08 22:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45887.1550627274</v>
+        <v>45887.15506273148</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,97 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45887.1550627274</v>
+        <v>45887.15506273148</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Mirandes –</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mirandes – HuescaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23/08 15:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+8,34%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45887.19505432273</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>51,4%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+2,72%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45887.19505432273</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>23/08 15:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45887.19505432273</v>
+        <v>45887.19505431713</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,97 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45887.19505432273</v>
+        <v>45887.19505431713</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | H 2 (−1.5) | Storm Hunt</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Storm Hunter – Maddison InglisWTA - US Open, Qualifications</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>H 2 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>18/08 19:40</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>69,7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45887.22677494321</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | IF Elfsbor</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IF Elfsborg – Halmstads BKAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24/08 14:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+0,86%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45887.22677494321</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>18/08 19:40</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45887.22677494321</v>
+        <v>45887.22677494213</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>50</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,142 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45887.22677494321</v>
+        <v>45887.22677494213</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Leeds – Ev</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Leeds – Everton385076e7 Angleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+8,00%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45887.27578620259</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sao Paulo – Atletico MineiroSérie A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>24/08 23:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+2,45%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45887.27578620259</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | 11-2 | Branstine,</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Branstine, Carson – Wang, XiyuEvénements. US Open (QF)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>18/08 21:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+0,16%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45887.27578620259</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4.75</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45887.27578620259</v>
+        <v>45887.2757862037</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>24/08 23:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45887.27578620259</v>
+        <v>45887.2757862037</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>18/08 21:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,97 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45887.27578620259</v>
+        <v>45887.2757862037</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 1X | Rot-Weiss </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Rot-Weiss Essen – DortmundAllemagne. Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18/08 18:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+4,14%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45887.30929584038</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Club BrugesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+3,64%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45887.30929584038</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>18/08 18:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45887.30929584038</v>
+        <v>45887.30929584491</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,187 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45887.30929584038</v>
+        <v>45887.30929584491</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova – FC Petrolul PloiestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24/08 15:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+32,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45887.35652589119</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs2e équipe | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mirassol – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>18/08 23:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+9,23%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45887.35652589119</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Basketball | H 2 (−2.5)4e période | Sénégal – </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sénégal – Soudan du SudInternational - AfroBasket</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)4e période</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18/08 18:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+2,76%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45887.35652589119</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Aris Thess</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Aris Thessalonique – VolosSuper League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/08 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+2,54%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45887.35652589119</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45887.35652589119</v>
+        <v>45887.35652589121</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>18/08 23:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45887.35652589119</v>
+        <v>45887.35652589121</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>18/08 18:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.15</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45887.35652589119</v>
+        <v>45887.35652589121</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,142 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45887.35652589119</v>
+        <v>45887.35652589121</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Nuno Borge</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nuno Borges – Kamil MajchrzakATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19/08 00:10</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45887.39528785468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2(2:0) | Tokyo Verd</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy – Sanfrecce HiroshimaJapon. Japon - J League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2(2:0)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/08 10:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+9,91%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45887.39528785468</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Tennis | 11-2 | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Luciano DarderiWinston Salem ATP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/08 18:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+2,34%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45887.39528785468</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>19/08 00:10</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45887.39528785468</v>
+        <v>45887.3952878588</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>11</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45887.39528785468</v>
+        <v>45887.3952878588</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>19/08 18:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.89</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,187 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45887.39528785468</v>
+        <v>45887.3952878588</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | AD Pasto –</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AD Pasto – Independiente MedellinPrimera A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/08 00:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+7,19%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45887.43497600484</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Differd</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FC Differdange 03 – Racing UnionNational Division</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>18/08 17:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+6,07%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45887.43497600484</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 3.5 - tir cadré2e équipe | Elche – Be</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Elche – Betis SévilleEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>56,1%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+3,85%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45887.43497600484</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Raphael Co</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Raphael Collignon – Nishesh BasavareddyATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18/08 18:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+1,35%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45887.43497600484</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>19/08 00:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45887.43497600484</v>
+        <v>45887.43497600695</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>18/08 17:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>35</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45887.43497600484</v>
+        <v>45887.43497600695</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.85</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45887.43497600484</v>
+        <v>45887.43497600695</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>18/08 18:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45887.43497600484</v>
+        <v>45887.43497600695</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 27.5 - tirs | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Sturm GrazEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+21,1%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45887.47226467064</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico J</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Atletico Junior – Atlético BucaramangaPrimera A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>18/08 22:15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45887.47226467064</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1.88</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45887.47226467064</v>
+        <v>45887.47226467593</v>
       </c>
     </row>
     <row r="52">
@@ -2657,23 +2655,156 @@
           <t>18/08 22:15</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45887.47226467593</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Breidablik</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Breidablik – SS VirtusLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+25,3%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45887.53453966698</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 2.51er set2e participant | Sorana Cir</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sorana Cirstea – Moyuka UchijimaWTA 250 Cleveland</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 2.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>18/08 15:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+6,16%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45887.53453966698</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Qingdao Ha</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Qingdao Hainiu FC – Shanghai ShenhuaSuper League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23/08 11:35</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>+17,7%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>45887.47226467064</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+5,90%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45887.53453966698</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>65</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45887.53453966698</v>
+        <v>45887.53453966435</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>18/08 15:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45887.53453966698</v>
+        <v>45887.53453966435</v>
       </c>
     </row>
     <row r="55">
@@ -2788,23 +2784,66 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>50</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+5,90%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45887.53453966435</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Martin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – Gimnasia La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>23/08 23:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>+5,90%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>45887.53453966698</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+4,91%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45887.56804282308</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,23 +2827,156 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>50</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+4,91%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45887.56804282407</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Real Madri</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+15,9%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45887.60054349163</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spezia – C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Spezia – CarrareseSerie B</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2,10%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>+4,91%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>45887.56804282308</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+5,97%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45887.60054349163</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Lincoln Re</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+5,20%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45887.60054349163</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3.4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45887.60054349163</v>
+        <v>45887.60054349537</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45887.60054349163</v>
+        <v>45887.60054349537</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>45</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,97 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45887.60054349163</v>
+        <v>45887.60054349537</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Leganes – </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Leganes – CadixLaLiga2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>22/08 19:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+24,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45887.64294892226</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 8.5 - tir cadré | Real Madri</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaLaLiga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+7,15%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45887.64294892226</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>22/08 19:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45887.64294892226</v>
+        <v>45887.64294892361</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,97 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45887.64294892226</v>
+        <v>45887.64294892361</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 5.5 - tir cadré1re équipe | Real Madri</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+7,42%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45887.68730510118</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Talia Gibs</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Talia Gibson – Greet MinnenWTA 250 Cleveland</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>18/08 16:40</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>36,0%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+6,12%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45887.68730510118</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3.7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45887.68730510118</v>
+        <v>45887.68730510417</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>18/08 16:40</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.95</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45887.68730510118</v>
+        <v>45887.68730510417</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Moins que 76.51re mi-temps | Golden Sta</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries – Phoenix MercuryÉtats-Unis - WNBA A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 76.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/08 02:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45887.72371122355</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2.4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,187 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45887.72371122355</v>
+        <v>45887.72371122685</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Connecticu</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Connecticut Sun – Washington MysticsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19/08 23:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+7,77%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45887.77367624655</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Ferencváro</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ferencvárosi TC – QarabağEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+5,98%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45887.77367624655</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 4.5 - tir cadré2e équipe | Elche – Be</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Elche – Betis SévilleEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+4,32%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45887.77367624655</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Celtic Gla</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Celtic Glasgow – Kairat AlmatyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+3,17%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45887.77367624655</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>19/08 23:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>25</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45887.77367624655</v>
+        <v>45887.77367625</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45887.77367624655</v>
+        <v>45887.77367625</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F67" t="n">
+        <v>2.7</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45887.77367624655</v>
+        <v>45887.77367625</v>
       </c>
     </row>
     <row r="68">
@@ -3349,10 +3343,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.8</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3365,7 +3357,97 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45887.77367624655</v>
+        <v>45887.77367625</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 13.5 - tirs1re équipe | Ferencvaro</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ferencvaros – Qarabag AgdamEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+5,55%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45887.80499372777</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | Moins que 38.54e période | Belgique –</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Belgique – FranceInternational - EuroBasket (H)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 38.54e période</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+4,00%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45887.80499372777</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F69" t="n">
+        <v>1.8</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45887.80499372777</v>
+        <v>45887.80499372685</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,52 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45887.80499372777</v>
+        <v>45887.80499372685</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20/08 02:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+15,6%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45887.84915499697</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,142 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45887.84915499697</v>
+        <v>45887.849155</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(17:0)P | Grande-Bre</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Grande-Bretagne – LituanieBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>X(17:0)P</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>27/08 10:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+5,57%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45887.8886451777</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Real Madri</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaLaLiga</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,34%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45887.8886451777</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | HJK Helsin</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HJK Helsinki – IFK MariehamnVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>24/08 12:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+4,28%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45887.8886451777</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>27/08 10:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
+      <c r="F72" t="n">
+        <v>18.75</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45887.8886451777</v>
+        <v>45887.88864517361</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45887.8886451777</v>
+        <v>45887.88864517361</v>
       </c>
     </row>
     <row r="74">
@@ -3605,23 +3601,156 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="n">
+        <v>60</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+4,28%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45887.88864517361</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dunajska S</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Dunajska Streda – AS TrencinFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>+4,28%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>45887.8886451777</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+41,3%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45887.92976228717</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | Real Madri</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+4,35%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45887.92976228717</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>20/08 02:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+4,16%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45887.92976228717</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-18.xlsx
+++ b/data/valuebets_database_2025-08-18.xlsx
@@ -3644,10 +3644,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>60</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45887.92976228717</v>
+        <v>45887.92976229166</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F76" t="n">
+        <v>2.25</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45887.92976228717</v>
+        <v>45887.92976229166</v>
       </c>
     </row>
     <row r="77">
@@ -3734,10 +3730,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>20</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3750,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45887.92976228717</v>
+        <v>45887.92976229166</v>
       </c>
     </row>
   </sheetData>
